--- a/data/trans_orig/IP2906_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25306</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>35564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46094</t>
+          <t>46547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59946</t>
+          <t>60177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60265</t>
+          <t>59609</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69555</t>
+          <t>69508</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111259</t>
+          <t>110443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126792</t>
+          <t>126956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59330</t>
+          <t>59092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75299</t>
+          <t>74982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67286</t>
+          <t>68247</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90803</t>
+          <t>90825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161670</t>
+          <t>160302</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>72,88%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20976</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36945</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32867</t>
+          <t>32845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>55423</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58275</t>
+          <t>59643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32044</t>
+          <t>31527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42775</t>
+          <t>42205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53589</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71045</t>
+          <t>70365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>35762</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21179</t>
+          <t>21749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>34950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48907</t>
+          <t>49587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66363</t>
+          <t>67280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32779</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38457</t>
+          <t>37974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64369</t>
+          <t>64888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>48624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>36829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59447</t>
+          <t>58407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77288</t>
+          <t>76769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103200</t>
+          <t>103683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>10221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20289</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22977</t>
+          <t>23353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>29949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28597</t>
+          <t>28648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36218</t>
+          <t>36271</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54440</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64665</t>
+          <t>64698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36334</t>
+          <t>36357</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30746</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41828</t>
+          <t>41380</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60775</t>
+          <t>60517</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75265</t>
+          <t>75924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35796</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>22871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>40499</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30171</t>
+          <t>30399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>54439</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58475</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88980</t>
+          <t>86658</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>81380</t>
+          <t>81357</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98716</t>
+          <t>98985</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100177</t>
+          <t>100141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124409</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>187456</t>
+          <t>189778</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217961</t>
+          <t>218466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,03%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>51798</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>71544</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67958</t>
+          <t>66959</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90278</t>
+          <t>88719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>125769</t>
+          <t>124580</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153879</t>
+          <t>155002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55924</t>
+          <t>56966</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75703</t>
+          <t>75670</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63586</t>
+          <t>65145</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85906</t>
+          <t>86905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>127453</t>
+          <t>126330</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>155563</t>
+          <t>156752</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,72%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>246961</t>
+          <t>247107</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>290031</t>
+          <t>288013</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>289224</t>
+          <t>290695</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>343369</t>
+          <t>342775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>543972</t>
+          <t>551504</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>617390</t>
+          <t>619270</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>327744</t>
+          <t>329762</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>370814</t>
+          <t>370668</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>395675</t>
+          <t>396269</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>449820</t>
+          <t>448349</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>739430</t>
+          <t>737550</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>812848</t>
+          <t>805316</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2906_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2906_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7825</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4485</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>17693</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11223</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24853</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>21952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>26727</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>17524</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35564</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52438</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47569</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55778</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>53707</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46547</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60177</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>75,22%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>65,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>84,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65573</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59609</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69508</t>
+          <t>43588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>119280</t>
+          <t>91162</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110443</t>
+          <t>84356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>126956</t>
+          <t>97662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>84,79%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72393</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60238</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>82478</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,39%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>53,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>67752</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>59092</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>74982</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>70,37%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>77,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>79980</t>
+          <t>64864</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68247</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90825</t>
+          <t>72537</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>147732</t>
+          <t>137257</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>132359</t>
+          <t>123851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160302</t>
+          <t>150032</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,65%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40030</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29945</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52185</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>28523</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21293</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>37183</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43690</t>
+          <t>29224</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32845</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>72213</t>
+          <t>69255</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59643</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87586</t>
+          <t>82661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>96275</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>96275</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>96275</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>219945</t>
+          <t>206512</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>219945</t>
+          <t>206512</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>219945</t>
+          <t>206512</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>32030</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26704</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37921</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>66,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25885</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20237</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31527</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>46,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>25562</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42205</t>
+          <t>30951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61767</t>
+          <t>57592</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52672</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70365</t>
+          <t>66118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24646</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18755</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>29972</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>30114</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24472</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35762</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>53,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>63,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>23587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>35405</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>53622</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49587</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67280</t>
+          <t>61512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56676</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56676</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56676</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63954</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25554</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15594</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35948</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,8%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25526</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19163</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33067</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>37,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>26289</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>19024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37040</t>
+          <t>33772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>51876</t>
+          <t>51843</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37974</t>
+          <t>39130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64888</t>
+          <t>63199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42830</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32436</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>52790</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,43%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>42261</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34720</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48624</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>47519</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36829</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58407</t>
+          <t>49400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>89781</t>
+          <t>84965</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76769</t>
+          <t>73609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103683</t>
+          <t>97678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7249</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11532</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,54%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>7126</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10847</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>20,84%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7666</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14306</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20289</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>32330</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28047</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35407</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,69%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>70,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,46%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>27074</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23353</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>29949</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>79,16%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>68,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33053</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28648</t>
+          <t>24457</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36271</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54630</t>
+          <t>55758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64698</t>
+          <t>64991</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>32230</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>26490</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>36799</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>68,27%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>56,11%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>77,95%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>32431</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>27615</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>36357</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>75,79%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>64,54%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>84,97%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36657</t>
+          <t>32705</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>27641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41380</t>
+          <t>36504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>69088</t>
+          <t>64935</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>58088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75924</t>
+          <t>71441</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>14979</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10410</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>20719</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>31,73%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>43,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10358</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6432</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15174</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>35,46%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>15139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>25054</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36054</t>
+          <t>31901</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>41083</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30857</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>53940</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>22,02%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>38,48%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>30587</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>22871</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>40499</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>18,77%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>33,24%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41323</t>
+          <t>28209</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30399</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54439</t>
+          <t>36447</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>71909</t>
+          <t>69292</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>56167</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86658</t>
+          <t>84699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,58%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>99081</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>86224</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>109307</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>70,69%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>61,52%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>77,98%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>91269</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>81357</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>98985</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>74,9%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>66,76%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>81,23%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>113257</t>
+          <t>91577</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100141</t>
+          <t>83339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>98602</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>204527</t>
+          <t>190658</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>189778</t>
+          <t>175251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>218466</t>
+          <t>203783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140164</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>121856</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>121856</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>121856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>119786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>119786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154580</t>
+          <t>119786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>276436</t>
+          <t>259950</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276436</t>
+          <t>259950</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>276436</t>
+          <t>259950</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>80085</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>68755</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>91432</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>51,13%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>43,89%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>58,37%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>61322</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>51798</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>70502</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>40,64%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>78649</t>
+          <t>65421</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>54927</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88719</t>
+          <t>75413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>139971</t>
+          <t>145505</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124580</t>
+          <t>130363</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>155002</t>
+          <t>161607</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>76557</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>65210</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>87887</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>48,87%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>41,63%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>56,11%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>66146</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>56966</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>75670</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>51,89%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>59,36%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>75215</t>
+          <t>70585</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65145</t>
+          <t>60593</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86905</t>
+          <t>81079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>141361</t>
+          <t>147143</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>126330</t>
+          <t>131041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>156752</t>
+          <t>162285</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,45%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>156642</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>156642</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>156642</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153864</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>153864</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153864</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>292648</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>292648</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>292648</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>298448</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>269880</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>323279</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>39,61%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>47,45%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>401</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>268322</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>247107</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>288013</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>43,43%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>315541</t>
+          <t>266306</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>290695</t>
+          <t>245993</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>342775</t>
+          <t>285743</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>583863</t>
+          <t>564755</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>551504</t>
+          <t>533428</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>619270</t>
+          <t>595068</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>382893</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>358062</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>411461</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>52,55%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>60,39%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>504</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>349453</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>329762</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>370668</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>423503</t>
+          <t>339608</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>396269</t>
+          <t>320171</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>448349</t>
+          <t>359921</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>772957</t>
+          <t>722500</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>737550</t>
+          <t>692187</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>805316</t>
+          <t>753827</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>905</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>617775</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>605914</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1356820</t>
+          <t>1287255</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
